--- a/EINPresswire-Report2-830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer-3.xlsx
+++ b/EINPresswire-Report2-830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer-3.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Media Outlets" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,6 +27,13 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -52,17 +59,20 @@
       <bottom style="thin"/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -425,8 +435,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B115"/>
+  <dimension ref="A1:B100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -443,1457 +457,1293 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AP N</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WPIX CW 11</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.globalfinanceherald.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MENAFN B</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>Economic News Observer</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.investornewsupdates.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IT P</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WHO NBC 13</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>http://www.financeindustrytoday.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WPIX CW 11
-E</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>Journal of Business News</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.globaltechtimes.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KTAB CBS 32 WCMH NBC 4
-A</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WNCT CBS 9</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.americantechtoday.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WTTK/WTTV CBS 4 KTVX ABC 4
-I</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>Innovation &amp; Entrepreneurs News</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.modernfinanceonline.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WHO NBC 13
-J</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WDAF FOX 4</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.personalwealthguide.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WBTW CBS 13 WTAJ CBS 10
-M</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>Global Reporter Journal</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.appliedtechnologynews.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WNCT CBS 9
-I</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WPRI CBS 12</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.conchovalleyhomepage.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WDAF FOX 4
-G</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>Corporate Crypto Times</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ksnt.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KLST CBS 8 KSNT NBC 27
-S</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WMBD CBS 31</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.corporatecryptotimes.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WPRI CBS 12
-C</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>European Globe</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wpri.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WLAX FOX 25/WEUX FOX 48 WKBN CBS 27
-L</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>KAMC ABC 28</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wiproud.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WMBD CBS 31
-E</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>European Morning Report</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wkbn.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KAMC ABC 28
-E</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>KTVI FOX 2</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.businesspostexaminer.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KTVI FOX 2
-T</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>The World Newswire</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marcomworld.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WMBB ABC 13
-T</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WMBB ABC 13</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.europeanglobe.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KFOR NBC 4 WFLA NBC 8
-O</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>The Consumer News Network</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.centralillinoisproud.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WATE ABC 6
-G</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WATE ABC 6</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.europeanmorning.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WREG CBS 3 WOOD NBC 8
-M</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>Global Business Watch</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.everythinglubbock.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>WCIA CBS 3 KSNW NBC 3
-C</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WHBF CBS 4</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>https://fox2now.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WHBF CBS 4
-E</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>European News Update</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theworldnewswire.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KCAU ABC 9
-C</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>KCAU ABC 9</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theconsumernewsnetwork.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>KSEE NBC 24 KDVR FOX 31
-F</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>Consumer Products World</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mypanhandle.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>WJHL ABC/CBS 11
-E</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WJHL ABC/CBS 11</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.worldreportmonitor.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WFXV FOX 33
-B</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>Euro Broadcast News</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.globalcybercurrencytimes.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KNWA NBC/FOX 51
-C</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WFXV FOX 33</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yourcentralvalley.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>WSPA CBS 7
-T</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>Business Times Journal</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>https://kdvr.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>WAVY NBC 10
-C</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>KNWA NBC/FOX 51</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wjhl.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KSN NBC/KODE ABC 12 WVLA NBC 33
-J</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>Consumer World Report</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.eurobroadcastnews.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>KOIN CBS 6
-S</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WSPA CBS 7</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnyhomepage.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>KHON CW/FOX 2 WPHL M</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>The European Gazette</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.businesstimesjournal.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TV 17
-H</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WAVY NBC 10</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.consumerworldreport.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>WWLP NBC/CW 22 WANE CBS 15
-C</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>Cryptocurrency Insider Today</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nwahomepage.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>WGHP FOX 8
-SMB W</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>KOIN CBS 6</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.centraleuropeonline.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KLRT FOX 16
-I</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>Small Business News Today</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.americantimesreporter.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KXMB CBS/CW 12
-PR W</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WGHP FOX 8</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wspa.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>WHNT CBS 19
-E</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>SMB World Report</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theeuropeangazette.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>WBRE NBC 28
-SMB &amp; M</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>KLRT FOX 16</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wavy.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KRON M</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>International Business Watch</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptocurrencyinsidertoday.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TV 4
-B</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>KXMB CBS/CW 12</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fourstateshomepage.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>WVNS FOX/CBS 59 WJBF ABC 6
-G</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>PR Wire India</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.louisianafirstnews.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KTXL FOX 40
-G</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WHNT CBS 19</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>https://prwireindia.com/press-release/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>WNTZ FOX 48
-C</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>Economic Policy Times</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kxnet.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>KFDX NBC 3
-T</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WBRE NBC 28</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>https://whnt.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>WTVO ABC 17
-M</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>SMB &amp; Me</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.economicpolicytimes.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>WROC CBS 8 WYTV ABC 33
-R</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>KRON MyNetworkTV 4</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.smbandme.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>WGN 9 WIVT ABC 34
-C</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>Business Herald Online</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.2822news.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>WLNS CBS 6 KWKT FOX 44
-L</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>KTXL FOX 40</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kron4.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>WDKY FOX 56
-C</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>Global Advertising News</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.businessheraldonline.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>WEHT ABC25/WTVW CW 7 KTAL NBC 6
-H</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WNTZ FOX 48</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wvnstv.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>WTEN ABC 10
-A</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>Crypto Times Gazette</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wjbf.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>WIAT CBS 42
-A</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>KFDX NBC 3</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>https://kalkinemedia.com/news/world-news/origyn-launches-icrc7icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>WDTN NBC 2
-E</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>The MarCom Journal</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.stateoftheunionnews.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>WJTV CBS 12
-S</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WTVO ABC 17</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.globaladvertisingnews.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>KIAH CW 39 WNCN CBS 17
-H</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>Montserrat Daily News</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>https://fox40.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>KMID ABC 2
-W</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WDKY FOX 56</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptotimesgazette.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>WSAV NBC 3 WKRG CBS 5
-S</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>Cybercurrency News Center</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cenlanow.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>KELO CBS 11 WSYR ABC 9
-S</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WTEN ABC 10</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tristatehomepage.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FOX 21
-C</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WIAT CBS 42</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ktalnews.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>KTSM NBC 9 KVEO NBC 23
-E</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>America News Observer</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.news10.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>WCBD NBC 2 KGET NBC 17/CW 12
-M</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WDTN NBC 2</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.americanewsobserver.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>WJET ABC 24 KDAF CW 33
-E</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>European Global Times</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cbs42.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>WFXR FOX 27
-E</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WJTV CBS 12</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wdtn.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>LEDGER
-WFFF FOX 44 WHTM ABC 27
-C</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>Small Business World Journal</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.europeanglobaltimes.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>WTNH ABC 8 WFRV CBS 5
-N</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>KMID ABC 2</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.smallbusinessworldjournal.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>KETK NBC 56/KFXK FOX 51
-N</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>World Advertising Report</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wjtv.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>WIVB CBS 4
-T</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>Coast To Coast Tribune</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>https://cw39.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>KSVI ABC 6 KREX CBS 5
-B</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WFXR FOX 27</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cbs17.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>WRIC ABC 8
-T</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>European Ledger</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.worldadvertisingreport.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>WJZY FOX 46 KOLR CBS 10
-C</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>LEDGER</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.europeanledger.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>KRQE CBS 13
-W</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>KETK NBC 56/KFXK FOX 51</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wfxrtv.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>KAMR NBC 4 KARK NBC 4
-A</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>North America Today</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mychamplainvalley.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>WDHN ABC 18
-E</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WIVB CBS 4</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.abc27.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>WKRN ABC 2
-T</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>Today In MarCom</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wtnh.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>KLAS CBS 8 KXAN NBC 36
-L</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WRIC ABC 8</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wearegreenbay.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>WJW FOX 8 WWTI ABC 50
-C</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>The America Watch</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.northamericatoday.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>KTVE NBC 10
-W</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>KRQE CBS 13</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ketk.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>WETM NBC 18 WGNO ABC 26
-E</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>World Cybercurrency News</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.todayinmarcom.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>WOWK CBS 13
-E</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WDHN ABC 18</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wivb.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>US D</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>European News Online</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.smallbusinessworldmagazine.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>US T</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WKRN ABC 2</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.globaljournalobserver.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>KLFY CBS 10
-C</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>The Global European</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yourbigsky.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>WXIN FOX 59
-US N</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>KTVE NBC 10</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.westernslopenow.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>WDVM 25
-C</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>World Online News Reports</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wric.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>WBOY ABC/NBC 12
-C</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WOWK CBS 13</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mytwintiers.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>WTRF ABC/CBS 7
-B</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>Eyeballs &amp; Clicks</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>https://wgno.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>WRBL CBS 3
-W</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>KLFY CBS 10</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.smallbusinessnewswatch.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EIN P</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>Crypto News Broadcast</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.growingbusinessesinthenews.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>IT I</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WXIN FOX 59</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.eyeballsandclicks.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BIS N</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>US National Times</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wowktv.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FOREX T</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>Cryptocurrency News Line</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.themarketingcommunicator.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>IPO N</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WBOY ABC/NBC 12</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.usdailyledger.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>NASDAQ N</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>Crypto Insider Review</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ustimesgazette.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>G20 N</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WTRF ABC/CBS 7</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.smartsbusinesswire.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EIN N</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>Blockchain News Online</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cryptonewsbroadcast.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BP E</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>WRBL CBS 3</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.klfy.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BIT N</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>World Post Reporter</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.usnationaltimes.com/article/830090048-origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EMS N</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>ABC N</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>PDF R</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>RSS
-V</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>CSV
-ORIGYN L</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>ICRC7/ICRC37</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>ORIGYN L</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>NEUCH</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>SWITZERLAND</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>EINP</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>ORIGYN</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>ORIGYN NEW NFT STANDARD
-K</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>ORIGYN -</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>RWA TOKENIZATION -</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>OGY CRYPTO -</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>PR D</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>URL_TBD</t>
+          <t>International World Times</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>https://fox59.com/business/press-releases/ein-presswire/830090048/origyn-launches-icrc7-icrc37-a-new-era-for-nfts-on-the-internet-computer</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" r:id="rId99"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>